--- a/secure_report/reports/テスト項目書_20260701.xlsx
+++ b/secure_report/reports/テスト項目書_20260701.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\proj\nichiben\secure_report\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46D0423F-8F0F-4A39-AD8D-3BB45E9CE014}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A464717-EE1C-4C2C-95C8-7A5898538D48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="テスト項目書 Ph.1-Ph.20" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="361">
   <si>
     <t>ID</t>
   </si>
@@ -163,14 +163,6 @@
     <t>受講者管理 詳細 / 講師管理 詳細 / 課題管理 詳細 / 動画管理 詳細 / 教材管理 詳細 / 図書館管理 詳細</t>
   </si>
   <si>
-    <t>/cms_student/detail/{id}, 
-/cms_teacher/detail/{id}, 
-/cms_issue/detail/{id}, 
-/cms_video/detail/{id}, 
-/cms_material/detail/{id}, 
-/cms_book_library/detail/{id}</t>
-  </si>
-  <si>
     <t>Ph.5, Ph.17</t>
   </si>
   <si>
@@ -183,9 +175,6 @@
 4. 受講者管理 詳細・講師管理 詳細・課題管理 詳細・動画管理 詳細・教材管理 詳細・図書館管理 詳細 の各画面で同様にアラートが発生しないことを確認する</t>
   </si>
   <si>
-    <t>&lt;img src=x onerror=alert('XSS-04')&gt;</t>
-  </si>
-  <si>
     <t>XSS-05</t>
   </si>
   <si>
@@ -207,9 +196,6 @@
 3. HTMLソースで &lt;option&gt; 内の講師名が htmlspecialchars() でエスケープされていることを確認する</t>
   </si>
   <si>
-    <t>講師 の名前フィールド（&lt;script&gt;alert();&lt;/script&gt;）</t>
-  </si>
-  <si>
     <t>ページ読み込み時にアラートが発生しない。HTMLソースで &lt;script&gt; にエスケープされている</t>
   </si>
   <si>
@@ -261,12 +247,6 @@
 2. onclick ハンドラでアラートが発生しないことを確認する</t>
   </si>
   <si>
-    <t>';alert('XSS-07')//&amp;ccno=1&amp;eid=1</t>
-  </si>
-  <si>
-    <t>アラートが発生しない。onclick内でエスケープされる</t>
-  </si>
-  <si>
     <t>未実施</t>
   </si>
   <si>
@@ -274,10 +254,6 @@
   </si>
   <si>
     <t>試験回答確認（PC版タイプ1/2） / スマホ版（UA変更でアクセス）</t>
-  </si>
-  <si>
-    <t>/exam/answer_check1.php,
-/exam/answer_check2.php</t>
   </si>
   <si>
     <t>Ph.13, Ph.19</t>
@@ -293,9 +269,6 @@
 5. スマホ版テンプレートが描画されアラートが発生しないことを確認する</t>
   </si>
   <si>
-    <t>javascript:alert('XSS-08')</t>
-  </si>
-  <si>
     <t>PC版・スマホ版ともにhref属性内でエスケープされ、javascript: スキームが HTML エスケープにより無効化される</t>
   </si>
   <si>
@@ -305,31 +278,15 @@
     <t>倫理研修トップ（PC版・スマホ版） / 問題 / 回答 / やり直し / 結果</t>
   </si>
   <si>
-    <t>/ethic_treaning/index.php, /ethic_treaning/question.php, /ethic_treaning/question_answer.php, /ethic_treaning/retry.php, /ethic_treaning/result.php</t>
-  </si>
-  <si>
     <t>Ph.13, Ph.15</t>
   </si>
   <si>
     <t>F-7</t>
   </si>
   <si>
-    <t>1. 倫理研修トップ（/ethic_treaning/index.php）の pid パラメータにテストデータを付けてアクセスする
-2. onclick および href 属性内でアラートが発生しないことを確認する
-3. 続いて /ethic_treaning/question.php・question_answer.php・retry.php・result.php でも同様に確認する
-4. スマホ版の確認: DevTools › ネットワーク条件（Network Conditions）でUser-Agentをスマートフォン向け（例: iPhone）に切り替え /ethic_treaning/index.php に再アクセスする
-5. スマホ版テンプレートが描画されアラートが発生しないことを確認する</t>
-  </si>
-  <si>
-    <t>';alert('XSS-09')//&amp;ccno=1</t>
-  </si>
-  <si>
     <t>PC版・スマホ版ともにアラートが発生しない。onclick / href 内で |escape:'javascript' が適用されている</t>
   </si>
   <si>
-    <t>XSS-10</t>
-  </si>
-  <si>
     <t>商品詳細 / 商品レビュー詳細 / 動画プレイヤー / 試験トップ（タイプ1・2） / アンケートトップ / 倫理研修トップ / 決済トップ</t>
   </si>
   <si>
@@ -337,15 +294,6 @@
   </si>
   <si>
     <t>F-6</t>
-  </si>
-  <si>
-    <t>1. ターミナルで実行: curl -H "Referer: javascript:alert(1)" https://nichibenren-stg2.alfcloud.com/product/detail.php?pid=1
-2. レスポンスHTML内の「戻る」リンクの href 属性を確認する
-3. javascript: スキームが href に出力されていないことを確認する（# またはデフォルトURLになること）
-4. 対象URLを変えて /player/index.php・/exam/index.php・/exam2/index.php・/ethic_treaning/index.php・/settlement/index.php でも同様に確認する</t>
-  </si>
-  <si>
-    <t>Referer: javascript:alert('XSS-10')</t>
   </si>
   <si>
     <t>javascript: スキームが拒否される。href に # またはデフォルト安全URL が設定される</t>
@@ -366,9 +314,6 @@
     <t>1. 受講者サイトの講座検索フォームで条件を設定して検索する
 2. search_set.php に遷移した後、JavaScriptアラートが発生しないことを確認する
 3. HTMLソースで検索条件が json_encode() で安全に出力されていることを確認する</t>
-  </si>
-  <si>
-    <t>"';alert('XSS-11')//</t>
   </si>
   <si>
     <t>アラートが発生しない。json_encode() でJSコンテキストがエスケープされている</t>
@@ -390,9 +335,6 @@
 2. 検索結果ページ（/search/index.php）でアラートが発生しないことを確認する
 3. HTMLソースでDB取得値が Smarty |escape されていることを確認する
 4. 続いて /mypage/favorite.php・/mypage/buy_list.php にアクセスし、同様にアラートが発生しないことを確認する</t>
-  </si>
-  <si>
-    <t>&lt;img src=x onerror=alert('XSS-12')&gt;</t>
   </si>
   <si>
     <t>アラートが発生しない。DB取得値が |escape されて表示される</t>
@@ -453,22 +395,12 @@
     <t>新着研修一覧 / 商品一覧 / 商品詳細 / 会場研修一覧 / ランキング / 検索 / 受講一覧2</t>
   </si>
   <si>
-    <t>/product/list_new_training.php, /product/list.php, /product/detail.php, /product/list_live_training.php, /ranking/index.php, /search/index.php, /mypage/lesson_list2.php</t>
-  </si>
-  <si>
     <t>Ph.22</t>
   </si>
   <si>
     <t>STU-XSS-15</t>
   </si>
   <si>
-    <t>1. CMS「弁護士会マスタ」管理画面から、いずれかの弁護士会名を「"&gt;&lt;img src=x onerror=alert('XSS-15')&gt;」に変更して保存する
-2. その弁護士会が主催する会場研修商品を用意し、/product/list_new_training.php にアクセスする
-3. 商品カードの「主催」欄でスクリプトが実行されないことを確認する
-4. HTMLソースで主催欄の弁護士会名が &amp;lt;img&amp;gt; にエスケープされていることを確認する
-5. /product/detail.php・/product/list.php・/search/index.php でも同様に確認する</t>
-  </si>
-  <si>
     <t>"&gt;&lt;img src=x onerror=alert('XSS-15')&gt;  ※ CMS弁護士会マスタ name フィールドに設定</t>
   </si>
   <si>
@@ -485,13 +417,6 @@
   </si>
   <si>
     <t>STU-XSS-16</t>
-  </si>
-  <si>
-    <t>1. CMS商品管理から、いずれかの商品の「商品説明」フィールドを「"&gt;&lt;img src=x onerror=alert('XSS-16')&gt;」に変更して保存する
-2. 受講者サイト /product/detail.php?pid={id} にアクセスする
-3. 商品説明欄でスクリプトが実行されないことを確認する
-4. HTMLソースで商品説明が &amp;lt;img&amp;gt; にエスケープされていることを確認する
-5. スマートフォン用テンプレートで表示した場合も同様に確認する</t>
   </si>
   <si>
     <t>"&gt;&lt;img src=x onerror=alert('XSS-16')&gt;  ※ CMS商品の「商品説明」フィールドに設定</t>
@@ -575,24 +500,10 @@
     <t>CSRF-04</t>
   </si>
   <si>
-    <t>決済全ページ / 問合せ確認 / 倫理研修回答・回答履歴 / 試験2系 / 会員登録 / 会員情報編集 / 退会申請</t>
-  </si>
-  <si>
-    <t>/settlement/*.php, /inquiry/conf.php, /ethic_treaning/question_answer.php, /ethic_treaning/answer_history.php, /exam2/index.php, /exam2/answer_*.php, /exam2/resubmit_*.php, /member/regist.php, /mypage/edit.php, /mypage/refusal.php</t>
-  </si>
-  <si>
     <t>Ph.8, Ph.12, Ph.16</t>
   </si>
   <si>
     <t>F-15</t>
-  </si>
-  <si>
-    <t>1. 各フォームページのHTMLソースを表示する（Ctrl+U）
-2. &lt;form&gt; タグ内にCSRFトークンの hidden input が含まれることを確認する
-3. /settlement/ 配下の全決済ページ（index.php・payment_card.php・payment_bank.php・payment_free.php・payment_cvs.php・payment_edy.php・payment_id.php・payment_payeasy.php・payment_suica.php・payment_webmoney.php）でCSRFトークン hidden input を確認する
-4. /inquiry/conf.php・/ethic_treaning/question_answer.php・/ethic_treaning/answer_history.php でも同様に確認する
-5. /exam2/index.php・answer_check.php・answer_save.php・resubmit_check.php・resubmit_exec.php でCSRFトークン hidden input を確認する
-6. /member/regist.php・/mypage/edit.php・/mypage/refusal.php でも同様に確認する</t>
   </si>
   <si>
     <t>各フォームの &lt;form&gt; 内に &lt;input type="hidden" name="csrf_test_name" value="…"&gt; が存在する</t>
@@ -726,24 +637,12 @@
     <t>動画プレイヤー /player/index.php・サンプル /player/sample.php</t>
   </si>
   <si>
-    <t>/player/index.php, /player/sample.php</t>
-  </si>
-  <si>
     <t>Ph.9</t>
   </si>
   <si>
     <t>F-8</t>
   </si>
   <si>
-    <t>1. 受講者として動画プレイヤーページ（/player/index.php）にアクセスする
-2. ページのHTMLソースを表示する（Ctrl+U）
-3. &lt;!--[ 形式のセッション値デバッグコメントが含まれていないことを確認する
-4. 続いて /player/sample.php にアクセスし同様に &lt;!--[ 形式のデバッグコメントが含まれていないことを確認する</t>
-  </si>
-  <si>
-    <t>&lt;!--[ 形式のセッション変数ダンプがHTMLソースに存在しない</t>
-  </si>
-  <si>
     <t>INFO-02</t>
   </si>
   <si>
@@ -757,9 +656,6 @@
   </si>
   <si>
     <t>決済トップ / クレジットカード決済 / 銀行振込 / 無料受講申込 / カード登録 / カード登録送信 / PayPal</t>
-  </si>
-  <si>
-    <t>/settlement/index.php, /settlement/payment_card.php, /settlement/payment_bank.php, /settlement/payment_free.php, /settlement/member_card.php, /settlement/member_card_regist.php, /settlement/payment_paypal.php</t>
   </si>
   <si>
     <t>F-12</t>
@@ -787,10 +683,6 @@
   </si>
   <si>
     <t>F-15b</t>
-  </si>
-  <si>
-    <t>1. https://api.nichibenren-stg2.alfcloud.com/debug.php に直接アクセスする
-2. 404 またはアクセス拒否が返ることを確認する</t>
   </si>
   <si>
     <t>— アクセステストのみ</t>
@@ -866,17 +758,7 @@
     <t>CMS-M-01〜03</t>
   </si>
   <si>
-    <t>1. ターミナルで実行: curl -I https://cms.nichibenren-stg2.alfcloud.com/
-2. （またはブラウザDevTools › Network › 任意リクエストを選択 › Response Headers を確認）
-3. Cross-Origin-Opener-Policy ヘッダーが存在することを確認する
-4. Cross-Origin-Resource-Policy ヘッダーが存在することを確認する
-5. Cross-Origin-Embedder-Policy ヘッダーが存在することを確認する</t>
-  </si>
-  <si>
     <t>curl -I https://cms.nichibenren-stg2.alfcloud.com/</t>
-  </si>
-  <si>
-    <t>Cross-Origin-Opener-Policy・Cross-Origin-Resource-Policy・Cross-Origin-Embedder-Policy の3ヘッダーがすべてレスポンスに存在する</t>
   </si>
   <si>
     <t>HDR-02</t>
@@ -900,13 +782,7 @@
     <t>curl -I https://nichibenren-stg2.alfcloud.com/</t>
   </si>
   <si>
-    <t>Cross-Origin-Opener-Policy・Cross-Origin-Resource-Policy の3ヘッダーがすべてレスポンスに存在する</t>
-  </si>
-  <si>
     <t>HDR-03</t>
-  </si>
-  <si>
-    <t>CMS-L-01</t>
   </si>
   <si>
     <t>1. ターミナルで実行: curl -I https://cms.nichibenren-stg2.alfcloud.com/
@@ -1020,11 +896,6 @@
     <t>#5</t>
   </si>
   <si>
-    <t>1. ブラウザまたは curl で https://nichibenren-stg2.alfcloud.com/login_sso.php?burl=https://evil.example.com にアクセスする
-2. 外部ドメイン（evil.example.com）へのリダイレクトが発生しないことを確認する
-3. エラーページまたはシステム内のデフォルトURLへ遷移することを確認する</t>
-  </si>
-  <si>
     <t>?burl=https://evil.example.com</t>
   </si>
   <si>
@@ -1038,11 +909,6 @@
   </si>
   <si>
     <t>/login_sso_new.php</t>
-  </si>
-  <si>
-    <t>1. ブラウザまたは curl で https://nichibenren-stg2.alfcloud.com/login_sso_new.php?burl=https://evil.example.com にアクセスする
-2. 外部ドメイン（evil.example.com）へのリダイレクトが発生しないことを確認する
-3. エラーページまたはシステム内のデフォルトURLへ遷移することを確認する</t>
   </si>
   <si>
     <t>INPUT-01</t>
@@ -1087,9 +953,6 @@
   <si>
     <t>1. 受講者サイトの検索フォームのPOSTパラメータをGETで付けてアクセスする: /search/index.php?keyword=testval
 2. GET パラメータが処理されていないことを確認する</t>
-  </si>
-  <si>
-    <t>URL: /search/index.php?keyword=testval</t>
   </si>
   <si>
     <t>GET パラメータが無視される。$_GET 値が検索結果に影響しない</t>
@@ -1292,6 +1155,203 @@
   <si>
     <t>`テスト&lt;script&gt;alert('XSS-17')&lt;/script&gt;` 
 ※ DB user.name フィールドに設定</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>/cms_student/detail/{id}, 
+/cms_teacher/detail/{id}, 
+/cms_issue/detail/{id}, 
+/cms_video/detail/{id}, 
+/cms_material/detail/{id}, 
+/cms_book_library/detail/{id}</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>&lt;img src=x onerror=alert('XSS-04')&gt;</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>講師 の名前フィールド（&lt;script&gt;alert();&lt;/script&gt;）</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>アラートが発生しない。onclick内でエスケープされる</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>/ethic_treaning/index.php, /ethic_treaning/question.php, /ethic_treaning/question_answer.php, /ethic_treaning/retry.php, /ethic_treaning/result.php</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>/exam/answer_check1.php,
+/exam/answer_check2.php</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>1. 倫理研修トップ（/ethic_treaning/index.php）の pid パラメータにテストデータを付けてアクセスする
+2. onclick および href 属性内でアラートが発生しないことを確認する
+3. 続いて /ethic_treaning/question.php・question_answer.php・retry.php・result.php でも同様に確認する
+4. スマホ版の確認: DevTools › ネットワーク条件（Network Conditions）でUser-Agentをスマートフォン向け（例: iPhone）に切り替え /ethic_treaning/index.php に再アクセスする
+5. スマホ版テンプレートが描画されアラートが発生しないことを確認する</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>;alert('XSS-07')//&amp;ccno=1&amp;eid=1</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>javascript:alert('XSS-08')</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>;alert('XSS-09')//&amp;pid=1</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>Referer: javascript:alert('XSS-10')</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>XSS-10</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>1. Chrom拡張`ModHeader` を用いて、Referer を javascript:alert() に変更する
+2. レスポンスHTML内の「戻る」リンクの href 属性を確認する
+3. javascript: スキームが href に出力されていないことを確認する（# またはデフォルトURLになること）
+4. 対象URLを変えて /player/index.php・/exam/index.php・/exam2/index.php・/ethic_treaning/index.php・/settlement/index.php でも同様に確認する</t>
+    <rPh sb="8" eb="10">
+      <t>カクチョウ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>モチ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>"';alert('XSS-11')//</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>&lt;img src=x onerror=alert('XSS-12')&gt;</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>1. 弁護士会マスタから、いずれかの弁護士会名を「"&gt;&lt;img src=x onerror=alert('XSS-15')&gt;」に変更して保存する
+2. その弁護士会が主催する会場研修商品を用意し、/product/list_new_training.php にアクセスする
+3. 商品カードの「主催」欄でスクリプトが実行されないことを確認する
+4. HTMLソースで主催欄の弁護士会名が &amp;lt;img&amp;gt; にエスケープされていることを確認する
+5. /product/detail.php・/product/list.php・/search/index.php でも同様に確認する</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>/product/list_new_training.php, /product/list.php, /product/detail.php, /product/list_live_training.php, /ranking/index.php, /search/index.php, /mypage/lesson_list2.php</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>1. CMS商品管理から、いずれかの商品の「商品説明」フィールドを「"&gt;&lt;img src=x onerror=alert('XSS-16')&gt;」に変更して保存する
+2. 受講者サイト /product/detail.php?pid={id} にアクセスする
+3. 商品説明欄でスクリプトが実行されないことを確認する
+4. HTMLソースで商品説明が &amp;lt;img&amp;gt; にエスケープされていることを確認する
+5. スマートフォン用テンプレートで表示した場合も同様に確認する</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>/inquiry/conf.php, /ethic_treaning/question_answer.php, /ethic_treaning/answer_history.php</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>1. 各フォームページのHTMLソースを表示する（Ctrl+U）
+2. &lt;form&gt; タグ内にCSRFトークンの hidden input が含まれることを確認する
+3. /inquiry/conf.php・/ethic_treaning/question_answer.php・/ethic_treaning/answer_history.php でCSRFトークン hidden input を確認する
+6. /mypage/edit.php でも同様に確認する</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t xml:space="preserve">問合せ確認 / 会員情報編集 </t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>&lt;!--[ 形式のセッション変数ダンプがHTMLソースに存在しない</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>/player/player_ethic.php</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>1. 受講者として動画プレイヤーページ（/player/player_ethic.php）にアクセスする
+2. ページのHTMLソースを表示する（Ctrl+U）
+3. &lt;!--[ 形式のセッション値デバッグコメントが含まれていないことを確認する</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>/settlement/index.php, /settlement/payment_card.php, /settlement/payment_bank.php, /settlement/payment_free.php, /settlement/member_card.php, /settlement/member_card_regist.php, /settlement/payment_paypal.php</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>現状決済系未使用</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンジョウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ケッサイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ケイ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ミシヨウ</t>
+    </rPh>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>1. https://api.nichibenren-stg2.alfcloud.com/debug.php に直接アクセスする
+2. 404 またはアクセス拒否が返ることを確認する</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>1. ターミナルで実行: curl -I https://cms.nichibenren-stg2.alfcloud.com/
+2. （またはブラウザDevTools › Network › 任意リクエストを選択 › Response Headers を確認）
+3. Cross-Origin-Opener-Policy ヘッダーが存在することを確認する
+4. Cross-Origin-Resource-Policy ヘッダーが存在することを確認する</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>Cross-Origin-Opener-Policy・Cross-Origin-Resource-Policy の2ヘッダーがすべてレスポンスに存在する</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>CMS-L-01</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>SSOのみのため検証不可</t>
+    <rPh sb="8" eb="10">
+      <t>ケンショウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>フカ</t>
+    </rPh>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>1. ブラウザまたは curl で https://nichibenren-stg2.alfcloud.com/login_sso.php?burl=https://evil.example.com にアクセスする
+2. 外部ドメイン（evil.example.com）へのリダイレクトが発生しないことを確認する
+3. エラーページまたはシステム内のデフォルトURLへ遷移することを確認する</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>1. ブラウザまたは curl で https://nichibenren-stg2.alfcloud.com/login_sso_new.php?burl=https://evil.example.com にアクセスする
+2. 外部ドメイン（evil.example.com）へのリダイレクトが発生しないことを確認する
+3. エラーページまたはシステム内のデフォルトURLへ遷移することを確認する</t>
+    <phoneticPr fontId="26"/>
+  </si>
+  <si>
+    <t>URL: /search/index.php?keyword=testval</t>
     <phoneticPr fontId="26"/>
   </si>
 </sst>
@@ -1824,7 +1884,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1954,19 +2014,28 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2448,19 +2517,19 @@
         <v>41</v>
       </c>
       <c r="E5" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="G5" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="H5" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="H5" s="7" t="s">
-        <v>45</v>
-      </c>
       <c r="I5" s="7" t="s">
-        <v>46</v>
+        <v>328</v>
       </c>
       <c r="J5" s="7" t="s">
         <v>30</v>
@@ -2472,7 +2541,7 @@
     </row>
     <row r="6" spans="1:12" ht="57" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>13</v>
@@ -2481,25 +2550,25 @@
         <v>14</v>
       </c>
       <c r="D6" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="G6" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="H6" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="I6" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="J6" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>54</v>
       </c>
       <c r="K6" s="6" t="s">
         <v>22</v>
@@ -2508,7 +2577,7 @@
     </row>
     <row r="7" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>13</v>
@@ -2517,36 +2586,36 @@
         <v>32</v>
       </c>
       <c r="D7" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="H7" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="I7" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="J7" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="K7" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="L7" s="7" t="s">
         <v>61</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>13</v>
@@ -2555,34 +2624,34 @@
         <v>32</v>
       </c>
       <c r="D8" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="H8" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="G8" s="5" t="s">
+      <c r="I8" s="50" t="s">
+        <v>334</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L8" s="5"/>
+    </row>
+    <row r="9" spans="1:12" ht="85.5" x14ac:dyDescent="0.15">
+      <c r="A9" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="K8" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="L8" s="5"/>
-    </row>
-    <row r="9" spans="1:12" ht="83.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="2" t="s">
-        <v>73</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>13</v>
@@ -2591,34 +2660,34 @@
         <v>32</v>
       </c>
       <c r="D9" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L9" s="7"/>
+    </row>
+    <row r="10" spans="1:12" ht="128.25" x14ac:dyDescent="0.15">
+      <c r="A10" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="L9" s="7"/>
-    </row>
-    <row r="10" spans="1:12" ht="83.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="2" t="s">
-        <v>81</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>13</v>
@@ -2627,34 +2696,34 @@
         <v>32</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>83</v>
+        <v>331</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>87</v>
+        <v>333</v>
+      </c>
+      <c r="I10" s="50" t="s">
+        <v>336</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="L10" s="5"/>
     </row>
-    <row r="11" spans="1:12" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:12" ht="85.5" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
-        <v>89</v>
+        <v>338</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>13</v>
@@ -2663,34 +2732,34 @@
         <v>32</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>93</v>
+        <v>339</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>94</v>
+        <v>337</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="L11" s="7"/>
     </row>
     <row r="12" spans="1:12" ht="53.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>13</v>
@@ -2699,25 +2768,25 @@
         <v>32</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>101</v>
+        <v>340</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="K12" s="6" t="s">
         <v>22</v>
@@ -2726,7 +2795,7 @@
     </row>
     <row r="13" spans="1:12" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>13</v>
@@ -2735,25 +2804,25 @@
         <v>32</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>35</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>108</v>
+        <v>341</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="K13" s="6" t="s">
         <v>22</v>
@@ -2762,43 +2831,43 @@
     </row>
     <row r="14" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="L14" s="10"/>
     </row>
     <row r="15" spans="1:12" ht="83.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="34" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="B15" s="35" t="s">
         <v>13</v>
@@ -2807,25 +2876,25 @@
         <v>32</v>
       </c>
       <c r="D15" s="37" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="E15" s="37" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="F15" s="37" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="G15" s="37" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="H15" s="37" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="I15" s="37" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="J15" s="37" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="K15" s="38" t="s">
         <v>22</v>
@@ -2834,7 +2903,7 @@
     </row>
     <row r="16" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="34" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="B16" s="35" t="s">
         <v>13</v>
@@ -2843,34 +2912,34 @@
         <v>32</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>126</v>
-      </c>
-      <c r="E16" s="37" t="s">
-        <v>127</v>
+        <v>111</v>
+      </c>
+      <c r="E16" s="51" t="s">
+        <v>343</v>
       </c>
       <c r="F16" s="37" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="G16" s="37" t="s">
-        <v>129</v>
-      </c>
-      <c r="H16" s="37" t="s">
-        <v>130</v>
+        <v>113</v>
+      </c>
+      <c r="H16" s="51" t="s">
+        <v>342</v>
       </c>
       <c r="I16" s="37" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="J16" s="37" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="K16" s="38" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="L16" s="37"/>
     </row>
     <row r="17" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="29" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="B17" s="30" t="s">
         <v>13</v>
@@ -2879,61 +2948,61 @@
         <v>32</v>
       </c>
       <c r="D17" s="32" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="E17" s="32" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="F17" s="32" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="G17" s="32" t="s">
-        <v>136</v>
-      </c>
-      <c r="H17" s="32" t="s">
-        <v>137</v>
+        <v>119</v>
+      </c>
+      <c r="H17" s="52" t="s">
+        <v>344</v>
       </c>
       <c r="I17" s="32" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="J17" s="32" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="K17" s="33" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="L17" s="32"/>
     </row>
     <row r="18" spans="1:12" ht="98.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="12" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="K18" s="6" t="s">
         <v>22</v>
@@ -2942,34 +3011,34 @@
     </row>
     <row r="19" spans="1:12" ht="57" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="12" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="K19" s="6" t="s">
         <v>22</v>
@@ -2978,34 +3047,34 @@
     </row>
     <row r="20" spans="1:12" ht="71.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="12" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="K20" s="6" t="s">
         <v>22</v>
@@ -3014,70 +3083,70 @@
     </row>
     <row r="21" spans="1:12" ht="171" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="12" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>32</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>162</v>
+        <v>347</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>163</v>
+        <v>345</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>166</v>
+        <v>346</v>
       </c>
       <c r="I21" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="J21" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="J21" s="5" t="s">
-        <v>167</v>
-      </c>
       <c r="K21" s="6" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="L21" s="5"/>
     </row>
     <row r="22" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="12" t="s">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>172</v>
+        <v>151</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="K22" s="6" t="s">
         <v>22</v>
@@ -3086,34 +3155,34 @@
     </row>
     <row r="23" spans="1:12" ht="42.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="12" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>32</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>177</v>
+        <v>156</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="K23" s="6" t="s">
         <v>22</v>
@@ -3122,799 +3191,803 @@
     </row>
     <row r="24" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="12" t="s">
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>187</v>
+        <v>166</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>189</v>
+        <v>168</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="L24" s="7"/>
     </row>
     <row r="25" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="12" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>192</v>
+        <v>171</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>193</v>
+        <v>172</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>195</v>
+        <v>174</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="L25" s="5"/>
     </row>
     <row r="26" spans="1:12" ht="57" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="14" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="G26" s="7" t="s">
         <v>18</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>201</v>
+        <v>180</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>202</v>
+        <v>181</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="L26" s="7"/>
     </row>
     <row r="27" spans="1:12" ht="71.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="16" t="s">
-        <v>204</v>
+        <v>183</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
       <c r="C27" s="8" t="s">
         <v>32</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>206</v>
+        <v>185</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>207</v>
+        <v>349</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>208</v>
+        <v>186</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>209</v>
+        <v>187</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>210</v>
+        <v>350</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>211</v>
+        <v>348</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="L27" s="5"/>
     </row>
     <row r="28" spans="1:12" ht="98.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="16" t="s">
-        <v>212</v>
+        <v>188</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>208</v>
+        <v>186</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>213</v>
+        <v>189</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>214</v>
+        <v>190</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="K28" s="11" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="L28" s="10"/>
     </row>
     <row r="29" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="16" t="s">
-        <v>215</v>
+        <v>191</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>32</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>217</v>
+        <v>351</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>208</v>
+        <v>186</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>218</v>
+        <v>193</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>219</v>
+        <v>194</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>220</v>
+        <v>195</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>221</v>
+        <v>196</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="L29" s="5"/>
+        <v>60</v>
+      </c>
+      <c r="L29" s="5" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="30" spans="1:12" ht="83.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="16" t="s">
-        <v>222</v>
+        <v>197</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>223</v>
+        <v>198</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>224</v>
+        <v>199</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>208</v>
+        <v>186</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>225</v>
+        <v>200</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>226</v>
+        <v>353</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>227</v>
+        <v>201</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="L30" s="7"/>
     </row>
-    <row r="31" spans="1:12" ht="128.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:12" ht="128.25" x14ac:dyDescent="0.15">
       <c r="A31" s="16" t="s">
-        <v>229</v>
+        <v>203</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>230</v>
+        <v>204</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>231</v>
+        <v>205</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>232</v>
+        <v>206</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>233</v>
+        <v>207</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>234</v>
+        <v>208</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>235</v>
+        <v>209</v>
       </c>
       <c r="K31" s="6" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="L31" s="5"/>
     </row>
     <row r="32" spans="1:12" ht="57" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="16" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>237</v>
+        <v>211</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>238</v>
+        <v>212</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>208</v>
+        <v>186</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>239</v>
+        <v>213</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>240</v>
+        <v>214</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>241</v>
+        <v>215</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>242</v>
+        <v>216</v>
       </c>
       <c r="K32" s="6" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="L32" s="7"/>
     </row>
     <row r="33" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="18" t="s">
-        <v>243</v>
+        <v>217</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>244</v>
+        <v>218</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>245</v>
+        <v>219</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>246</v>
+        <v>220</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>247</v>
+        <v>221</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>248</v>
+        <v>222</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>249</v>
+        <v>354</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>250</v>
+        <v>223</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>251</v>
+        <v>355</v>
       </c>
       <c r="K33" s="6" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="L33" s="5"/>
     </row>
-    <row r="34" spans="1:12" ht="71.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:12" ht="71.25" x14ac:dyDescent="0.15">
       <c r="A34" s="18" t="s">
-        <v>252</v>
+        <v>224</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>244</v>
+        <v>218</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>32</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>253</v>
+        <v>225</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>254</v>
+        <v>226</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>247</v>
+        <v>221</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>257</v>
+        <v>229</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>258</v>
+        <v>355</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="L34" s="7"/>
     </row>
-    <row r="35" spans="1:12" ht="57" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:12" ht="57" x14ac:dyDescent="0.15">
       <c r="A35" s="18" t="s">
-        <v>259</v>
+        <v>230</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>244</v>
+        <v>218</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>245</v>
+        <v>219</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>246</v>
+        <v>220</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>247</v>
+        <v>221</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>260</v>
+        <v>356</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>261</v>
+        <v>231</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>250</v>
+        <v>223</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>262</v>
+        <v>232</v>
       </c>
       <c r="K35" s="6" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="L35" s="5"/>
     </row>
     <row r="36" spans="1:12" ht="57" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="18" t="s">
-        <v>263</v>
+        <v>233</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>244</v>
+        <v>218</v>
       </c>
       <c r="C36" s="8" t="s">
         <v>32</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>253</v>
+        <v>225</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>254</v>
+        <v>226</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>247</v>
+        <v>221</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>264</v>
+        <v>234</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>265</v>
+        <v>235</v>
       </c>
       <c r="I36" s="7" t="s">
-        <v>257</v>
+        <v>229</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>262</v>
+        <v>232</v>
       </c>
       <c r="K36" s="6" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="L36" s="7"/>
     </row>
     <row r="37" spans="1:12" ht="71.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="18" t="s">
-        <v>266</v>
+        <v>236</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>244</v>
+        <v>218</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>267</v>
+        <v>237</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>268</v>
+        <v>238</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>269</v>
+        <v>239</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>271</v>
+        <v>241</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>272</v>
+        <v>242</v>
       </c>
       <c r="J37" s="5" t="s">
-        <v>273</v>
+        <v>243</v>
       </c>
       <c r="K37" s="6" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="L37" s="5"/>
     </row>
     <row r="38" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="20" t="s">
-        <v>274</v>
+        <v>244</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>275</v>
+        <v>245</v>
       </c>
       <c r="C38" s="8" t="s">
         <v>32</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>276</v>
+        <v>246</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>277</v>
+        <v>247</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>278</v>
+        <v>248</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>279</v>
+        <v>249</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="I38" s="7" t="s">
-        <v>281</v>
+        <v>251</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>282</v>
+        <v>252</v>
       </c>
       <c r="K38" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="L38" s="7"/>
+        <v>60</v>
+      </c>
+      <c r="L38" s="7" t="s">
+        <v>357</v>
+      </c>
     </row>
     <row r="39" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="20" t="s">
-        <v>283</v>
+        <v>253</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>275</v>
+        <v>245</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>284</v>
+        <v>254</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>285</v>
+        <v>255</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>286</v>
+        <v>256</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>287</v>
+        <v>257</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>281</v>
+        <v>251</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>282</v>
+        <v>252</v>
       </c>
       <c r="K39" s="6" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="L39" s="5"/>
     </row>
     <row r="40" spans="1:12" ht="57" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="21" t="s">
-        <v>288</v>
+        <v>258</v>
       </c>
       <c r="B40" s="22" t="s">
-        <v>289</v>
+        <v>259</v>
       </c>
       <c r="C40" s="8" t="s">
         <v>32</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>290</v>
+        <v>260</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>291</v>
+        <v>261</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>292</v>
+        <v>262</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>293</v>
+        <v>358</v>
       </c>
       <c r="I40" s="7" t="s">
-        <v>294</v>
+        <v>263</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>295</v>
+        <v>264</v>
       </c>
       <c r="K40" s="6" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="L40" s="7"/>
     </row>
     <row r="41" spans="1:12" ht="57" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="21" t="s">
-        <v>296</v>
+        <v>265</v>
       </c>
       <c r="B41" s="22" t="s">
-        <v>289</v>
+        <v>259</v>
       </c>
       <c r="C41" s="8" t="s">
         <v>32</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>297</v>
+        <v>266</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>298</v>
+        <v>267</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>292</v>
+        <v>262</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>299</v>
+        <v>359</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>294</v>
+        <v>263</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>295</v>
+        <v>264</v>
       </c>
       <c r="K41" s="6" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="L41" s="5"/>
     </row>
     <row r="42" spans="1:12" ht="57" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="23" t="s">
-        <v>300</v>
+        <v>268</v>
       </c>
       <c r="B42" s="24" t="s">
-        <v>301</v>
+        <v>269</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>302</v>
+        <v>270</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>303</v>
+        <v>271</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>304</v>
+        <v>272</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>305</v>
+        <v>273</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>306</v>
+        <v>274</v>
       </c>
       <c r="I42" s="7" t="s">
-        <v>307</v>
+        <v>275</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>308</v>
+        <v>276</v>
       </c>
       <c r="K42" s="6" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="L42" s="7"/>
     </row>
     <row r="43" spans="1:12" ht="42.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="23" t="s">
-        <v>309</v>
+        <v>277</v>
       </c>
       <c r="B43" s="24" t="s">
-        <v>301</v>
+        <v>269</v>
       </c>
       <c r="C43" s="8" t="s">
         <v>32</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>310</v>
+        <v>278</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>311</v>
+        <v>279</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>304</v>
+        <v>272</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>312</v>
+        <v>280</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>313</v>
+        <v>281</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>314</v>
+        <v>360</v>
       </c>
       <c r="J43" s="5" t="s">
-        <v>315</v>
+        <v>282</v>
       </c>
       <c r="K43" s="6" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="L43" s="5"/>
     </row>
     <row r="44" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="23" t="s">
-        <v>316</v>
+        <v>283</v>
       </c>
       <c r="B44" s="24" t="s">
-        <v>301</v>
+        <v>269</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>317</v>
+        <v>284</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>318</v>
+        <v>285</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>304</v>
+        <v>272</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>319</v>
+        <v>286</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>320</v>
+        <v>287</v>
       </c>
       <c r="I44" s="7" t="s">
-        <v>321</v>
+        <v>288</v>
       </c>
       <c r="J44" s="7" t="s">
-        <v>322</v>
+        <v>289</v>
       </c>
       <c r="K44" s="6" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="L44" s="7"/>
     </row>
     <row r="45" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="41" t="s">
-        <v>323</v>
+        <v>290</v>
       </c>
       <c r="B45" s="42" t="s">
-        <v>324</v>
+        <v>291</v>
       </c>
       <c r="C45" s="43" t="s">
         <v>32</v>
       </c>
       <c r="D45" s="44" t="s">
-        <v>325</v>
+        <v>292</v>
       </c>
       <c r="E45" s="44" t="s">
-        <v>326</v>
+        <v>293</v>
       </c>
       <c r="F45" s="44" t="s">
-        <v>327</v>
+        <v>294</v>
       </c>
       <c r="G45" s="44" t="s">
-        <v>328</v>
+        <v>295</v>
       </c>
       <c r="H45" s="44" t="s">
-        <v>329</v>
+        <v>296</v>
       </c>
       <c r="I45" s="44" t="s">
-        <v>330</v>
+        <v>297</v>
       </c>
       <c r="J45" s="44" t="s">
-        <v>331</v>
+        <v>298</v>
       </c>
       <c r="K45" s="6" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="L45" s="5"/>
     </row>
     <row r="46" spans="1:12" ht="98.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="45" t="s">
-        <v>332</v>
+        <v>299</v>
       </c>
       <c r="B46" s="46" t="s">
         <v>13</v>
@@ -3923,34 +3996,34 @@
         <v>32</v>
       </c>
       <c r="D46" s="48" t="s">
-        <v>350</v>
+        <v>317</v>
       </c>
       <c r="E46" s="48" t="s">
-        <v>349</v>
+        <v>316</v>
       </c>
       <c r="F46" s="49" t="s">
-        <v>333</v>
+        <v>300</v>
       </c>
       <c r="G46" s="49" t="s">
-        <v>334</v>
+        <v>301</v>
       </c>
       <c r="H46" s="48" t="s">
-        <v>355</v>
+        <v>322</v>
       </c>
       <c r="I46" s="48" t="s">
-        <v>359</v>
+        <v>326</v>
       </c>
       <c r="J46" s="49" t="s">
-        <v>335</v>
+        <v>302</v>
       </c>
       <c r="K46" s="40" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="L46" s="39"/>
     </row>
     <row r="47" spans="1:12" ht="114" x14ac:dyDescent="0.15">
       <c r="A47" s="45" t="s">
-        <v>336</v>
+        <v>303</v>
       </c>
       <c r="B47" s="46" t="s">
         <v>13</v>
@@ -3959,34 +4032,34 @@
         <v>32</v>
       </c>
       <c r="D47" s="48" t="s">
-        <v>352</v>
+        <v>319</v>
       </c>
       <c r="E47" s="48" t="s">
-        <v>351</v>
+        <v>318</v>
       </c>
       <c r="F47" s="49" t="s">
-        <v>333</v>
+        <v>300</v>
       </c>
       <c r="G47" s="49" t="s">
-        <v>337</v>
+        <v>304</v>
       </c>
       <c r="H47" s="48" t="s">
-        <v>356</v>
+        <v>323</v>
       </c>
       <c r="I47" s="48" t="s">
-        <v>358</v>
+        <v>325</v>
       </c>
       <c r="J47" s="49" t="s">
-        <v>338</v>
+        <v>305</v>
       </c>
       <c r="K47" s="40" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="L47" s="39"/>
     </row>
     <row r="48" spans="1:12" ht="98.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="45" t="s">
-        <v>339</v>
+        <v>306</v>
       </c>
       <c r="B48" s="46" t="s">
         <v>13</v>
@@ -3995,28 +4068,28 @@
         <v>32</v>
       </c>
       <c r="D48" s="48" t="s">
-        <v>354</v>
+        <v>321</v>
       </c>
       <c r="E48" s="48" t="s">
-        <v>353</v>
+        <v>320</v>
       </c>
       <c r="F48" s="49" t="s">
-        <v>333</v>
+        <v>300</v>
       </c>
       <c r="G48" s="49" t="s">
-        <v>340</v>
+        <v>307</v>
       </c>
       <c r="H48" s="48" t="s">
-        <v>357</v>
+        <v>324</v>
       </c>
       <c r="I48" s="49" t="s">
-        <v>341</v>
+        <v>308</v>
       </c>
       <c r="J48" s="49" t="s">
-        <v>342</v>
+        <v>309</v>
       </c>
       <c r="K48" s="40" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="L48" s="39"/>
     </row>
@@ -4043,7 +4116,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="25" t="s">
-        <v>343</v>
+        <v>310</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4051,7 +4124,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>344</v>
+        <v>311</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -4059,7 +4132,7 @@
         <v>32</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>345</v>
+        <v>312</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -4067,23 +4140,23 @@
         <v>14</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>346</v>
+        <v>313</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="27" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>347</v>
+        <v>314</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="28" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>348</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
